--- a/Biolage Prophet Output.xlsx
+++ b/Biolage Prophet Output.xlsx
@@ -10806,18 +10806,10 @@
       <c r="C415" t="n">
         <v>150</v>
       </c>
-      <c r="D415" t="n">
-        <v>1062.9526824</v>
-      </c>
-      <c r="E415" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F415" t="n">
-        <v>-13667.67028245558</v>
-      </c>
-      <c r="G415" t="n">
-        <v>152.70410359314</v>
-      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -10831,18 +10823,10 @@
       <c r="C416" t="n">
         <v>102</v>
       </c>
-      <c r="D416" t="n">
-        <v>1199.362967442857</v>
-      </c>
-      <c r="E416" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F416" t="n">
-        <v>-13870.32949178525</v>
-      </c>
-      <c r="G416" t="n">
-        <v>86.45517930632241</v>
-      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -10856,18 +10840,10 @@
       <c r="C417" t="n">
         <v>1490</v>
       </c>
-      <c r="D417" t="n">
-        <v>1335.773252443285</v>
-      </c>
-      <c r="E417" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F417" t="n">
-        <v>-12574.00440989274</v>
-      </c>
-      <c r="G417" t="n">
-        <v>1519.190546199265</v>
-      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -10881,18 +10857,10 @@
       <c r="C418" t="n">
         <v>2610</v>
       </c>
-      <c r="D418" t="n">
-        <v>1472.183537407996</v>
-      </c>
-      <c r="E418" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F418" t="n">
-        <v>-11620.77428219859</v>
-      </c>
-      <c r="G418" t="n">
-        <v>2608.830958858121</v>
-      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -10906,18 +10874,10 @@
       <c r="C419" t="n">
         <v>3710</v>
       </c>
-      <c r="D419" t="n">
-        <v>1608.593822387685</v>
-      </c>
-      <c r="E419" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F419" t="n">
-        <v>-10756.64566466743</v>
-      </c>
-      <c r="G419" t="n">
-        <v>3609.369861368968</v>
-      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -10931,18 +10891,10 @@
       <c r="C420" t="n">
         <v>4515</v>
       </c>
-      <c r="D420" t="n">
-        <v>1745.004107364081</v>
-      </c>
-      <c r="E420" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F420" t="n">
-        <v>-9785.38040300445</v>
-      </c>
-      <c r="G420" t="n">
-        <v>4717.045408008347</v>
-      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10956,18 +10908,10 @@
       <c r="C421" t="n">
         <v>5878</v>
       </c>
-      <c r="D421" t="n">
-        <v>1881.414392362338</v>
-      </c>
-      <c r="E421" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F421" t="n">
-        <v>-8904.300070045263</v>
-      </c>
-      <c r="G421" t="n">
-        <v>5734.53602596579</v>
-      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -10981,18 +10925,10 @@
       <c r="C422" t="n">
         <v>6781</v>
       </c>
-      <c r="D422" t="n">
-        <v>2017.824677407263</v>
-      </c>
-      <c r="E422" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F422" t="n">
-        <v>-8134.628953993613</v>
-      </c>
-      <c r="G422" t="n">
-        <v>6640.617427062367</v>
-      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -11006,18 +10942,10 @@
       <c r="C423" t="n">
         <v>6914</v>
       </c>
-      <c r="D423" t="n">
-        <v>2154.234962429433</v>
-      </c>
-      <c r="E423" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F423" t="n">
-        <v>-7514.231401165893</v>
-      </c>
-      <c r="G423" t="n">
-        <v>7397.425264912258</v>
-      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -11031,18 +10959,10 @@
       <c r="C424" t="n">
         <v>8340</v>
       </c>
-      <c r="D424" t="n">
-        <v>2290.645247426353</v>
-      </c>
-      <c r="E424" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F424" t="n">
-        <v>-7339.926195127669</v>
-      </c>
-      <c r="G424" t="n">
-        <v>7708.140755947402</v>
-      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -11056,18 +10976,10 @@
       <c r="C425" t="n">
         <v>7141</v>
       </c>
-      <c r="D425" t="n">
-        <v>2427.055532471232</v>
-      </c>
-      <c r="E425" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F425" t="n">
-        <v>-7536.528667184773</v>
-      </c>
-      <c r="G425" t="n">
-        <v>7647.948568935177</v>
-      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -11081,18 +10993,10 @@
       <c r="C426" t="n">
         <v>8107</v>
       </c>
-      <c r="D426" t="n">
-        <v>2563.465817474432</v>
-      </c>
-      <c r="E426" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F426" t="n">
-        <v>-7473.769067417035</v>
-      </c>
-      <c r="G426" t="n">
-        <v>7847.118453706114</v>
-      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -11106,18 +11010,10 @@
       <c r="C427" t="n">
         <v>8097</v>
       </c>
-      <c r="D427" t="n">
-        <v>2699.876102438293</v>
-      </c>
-      <c r="E427" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F427" t="n">
-        <v>-7283.56538755854</v>
-      </c>
-      <c r="G427" t="n">
-        <v>8173.73241852847</v>
-      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -11131,18 +11027,10 @@
       <c r="C428" t="n">
         <v>7384</v>
       </c>
-      <c r="D428" t="n">
-        <v>2836.286387402154</v>
-      </c>
-      <c r="E428" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F428" t="n">
-        <v>-8216.650354727388</v>
-      </c>
-      <c r="G428" t="n">
-        <v>7377.057736323484</v>
-      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -11156,18 +11044,10 @@
       <c r="C429" t="n">
         <v>6467</v>
       </c>
-      <c r="D429" t="n">
-        <v>2972.696672366015</v>
-      </c>
-      <c r="E429" t="n">
-        <v>12757.42170364872</v>
-      </c>
-      <c r="F429" t="n">
-        <v>-9264.140377859041</v>
-      </c>
-      <c r="G429" t="n">
-        <v>6465.977998155691</v>
-      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
